--- a/assets/Org_Structure_Template_EN.xlsx
+++ b/assets/Org_Structure_Template_EN.xlsx
@@ -1,285 +1,190 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12280"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="29400" windowHeight="12280" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Department List" sheetId="1" r:id="rId1"/>
-    <sheet name="Example" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Department List" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Example" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="24">
-  <si>
-    <t>Node Color</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Department</t>
-  </si>
-  <si>
-    <t>Leader</t>
-  </si>
-  <si>
-    <t>Department Function</t>
-  </si>
-  <si>
-    <t>Headcount</t>
-  </si>
-  <si>
-    <t>Management</t>
-  </si>
-  <si>
-    <t>Parent Department</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Technology Department</t>
-  </si>
-  <si>
-    <t>Ivan</t>
-  </si>
-  <si>
-    <t>R&amp;D and platform</t>
-  </si>
-  <si>
-    <t>——</t>
-  </si>
-  <si>
-    <t>(Top level, no parent)</t>
-  </si>
-  <si>
-    <t>Backend Team</t>
-  </si>
-  <si>
-    <t>Jack</t>
-  </si>
-  <si>
-    <t>Backend services</t>
-  </si>
-  <si>
-    <t>Direct Management</t>
-  </si>
-  <si>
-    <t>Frontend Team</t>
-  </si>
-  <si>
-    <t>Kate</t>
-  </si>
-  <si>
-    <t>Web &amp; client</t>
-  </si>
-  <si>
-    <t>Backend Team - Infra</t>
-  </si>
-  <si>
-    <t>Leo</t>
-  </si>
-  <si>
-    <t>Infrastructure &amp; SRE</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="22">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Arial Regular"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <name val="Arial Regular"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
+      <color theme="0"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
       <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <b val="1"/>
       <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <b val="1"/>
       <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <b val="1"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="36">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -598,164 +503,164 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -809,11 +714,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1100,235 +1068,543 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="12" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.61538461538461" style="2" customWidth="1"/>
-    <col min="3" max="3" width="31.0769230769231" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.8557692307692" style="2" customWidth="1"/>
-    <col min="5" max="5" width="32" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.4903846153846" style="2" customWidth="1"/>
-    <col min="7" max="7" width="20" style="1" customWidth="1"/>
-    <col min="8" max="8" width="30" style="1" customWidth="1"/>
-    <col min="9" max="9" width="36" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col width="12" customWidth="1" style="7" min="1" max="1"/>
+    <col width="9.61538461538461" customWidth="1" style="2" min="2" max="2"/>
+    <col width="31.0769230769231" customWidth="1" style="7" min="3" max="3"/>
+    <col width="15.8557692307692" customWidth="1" style="2" min="4" max="4"/>
+    <col width="32" customWidth="1" style="7" min="5" max="5"/>
+    <col width="16.4903846153846" customWidth="1" style="2" min="6" max="6"/>
+    <col width="20" customWidth="1" style="7" min="7" max="7"/>
+    <col width="30" customWidth="1" style="7" min="8" max="8"/>
+    <col width="36" customWidth="1" style="7" min="9" max="9"/>
+    <col width="9" customWidth="1" style="7" min="10" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17" spans="1:9">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
+    <row r="1" ht="17" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Node Color</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Department Function</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Headcount</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Parent Department</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="12" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.61538461538461" style="2" customWidth="1"/>
-    <col min="3" max="3" width="31.0769230769231" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.8557692307692" style="2" customWidth="1"/>
-    <col min="5" max="5" width="32" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.4903846153846" style="2" customWidth="1"/>
-    <col min="7" max="7" width="20" style="1" customWidth="1"/>
-    <col min="8" max="8" width="30" style="1" customWidth="1"/>
-    <col min="9" max="9" width="36" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col width="12" customWidth="1" style="7" min="1" max="1"/>
+    <col width="9.61538461538461" customWidth="1" style="2" min="2" max="2"/>
+    <col width="31.0769230769231" customWidth="1" style="7" min="3" max="3"/>
+    <col width="15.8557692307692" customWidth="1" style="2" min="4" max="4"/>
+    <col width="32" customWidth="1" style="7" min="5" max="5"/>
+    <col width="16.4903846153846" customWidth="1" style="2" min="6" max="6"/>
+    <col width="20" customWidth="1" style="7" min="7" max="7"/>
+    <col width="30" customWidth="1" style="7" min="8" max="8"/>
+    <col width="36" customWidth="1" style="7" min="9" max="9"/>
+    <col width="9" customWidth="1" style="7" min="10" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="17" spans="1:9">
-      <c r="A1" s="3" t="s">
+    <row r="1" ht="17" customFormat="1" customHeight="1" s="7">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Node Color</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Department Function</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Headcount</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Parent Department</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" customFormat="1" s="7">
+      <c r="B2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ABC Group Holdings</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>A. Anderson</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Global headquarters · New York, USA</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>——</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Top level, no parent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" customFormat="1" s="7">
+      <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ABC Americas</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>B. Brown</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Americas regional HQ · USA</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>120</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Direct Management</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ABC Group Holdings</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" customFormat="1" s="7">
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ABC APAC</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>C. Chen</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Asia-Pacific regional HQ · Singapore</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>150</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Direct Management</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ABC Group Holdings</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" customFormat="1" s="7">
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ABC EMEA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>D. Davies</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Europe &amp; Middle East HQ · UK</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>98</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Direct Management</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ABC Group Holdings</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" customFormat="1" s="7">
+      <c r="B6" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ABC US Operations</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>E. Evans</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>US field operations · Chicago</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>60</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Direct Management</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ABC Americas</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" customFormat="1" s="7">
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ABC China Operations</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>F. Fang</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>China operations · Shanghai</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>80</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Direct Management</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ABC APAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" customFormat="1" s="7">
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ABC Japan Operations</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>G. Goto</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Japan operations · Tokyo</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>35</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Direct Management</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ABC APAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" customFormat="1" s="7">
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ABC Germany Office</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>H. Hoffmann</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Germany office · Berlin</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>22</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Direct Management</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ABC EMEA</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>US Operations - Finance Center</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>I. Irving</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Finance shared services</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>12</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Direct Management</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ABC US Operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>China Ops - Finance Center</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>J. Jiang</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Finance &amp; tax shared services</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>15</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Direct Management</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ABC China Operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>China Ops - HR Center</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>K. Kong</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>HR shared services</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Direct Management</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ABC China Operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Japan Ops - Finance Team</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>L. Lee</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Local finance &amp; reporting</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:9">
-      <c r="A2" s="4"/>
-      <c r="B2" s="2">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="2">
-        <v>80</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:9">
-      <c r="A3" s="5"/>
-      <c r="B3" s="2">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="2">
-        <v>30</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:9">
-      <c r="A4" s="5"/>
-      <c r="B4" s="2">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="2">
-        <v>20</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:9">
-      <c r="A5" s="6"/>
-      <c r="B5" s="2">
-        <v>2</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="2">
-        <v>8</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:9">
-      <c r="A6" s="7"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:9">
-      <c r="A7" s="7"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:9">
-      <c r="A8" s="7"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:9">
-      <c r="A9" s="7"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="2"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Direct Management</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ABC Japan Operations</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>